--- a/Documents/BusinessAnalysis/成交条件样板库/成交条件样板库查询API调用说明.xlsx
+++ b/Documents/BusinessAnalysis/成交条件样板库/成交条件样板库查询API调用说明.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         <is>
           <t>var request = new OrganizationRequest("mcs_QueryTradeStPayTerm");
 request["mcs_buid"] = "BU-1018";
-request["mcs_subid"] = "A000025";
+request["mcs_subid"] = "SUB-001";
 request["mcs_countrycode"] = "001";
 request["mcs_prdgroupid"] = "4";
-request["mcs_buyercode"] = "ACN202605280000";
+request["mcs_buyercode"] = "0000016233"; // 客户编号（mcs_sapnumber）
 var response = service.Execute(request);
 var status = response["status"]?.ToString();
 var message = response["message"]?.ToString();
@@ -994,10 +994,10 @@
         <is>
           <t>var request = {
     mcs_buid: "BU-1018",
-    mcs_subid: "A000025",
+    mcs_subid: "SUB-001",
     mcs_countrycode: "001",
     mcs_prdgroupid: "4",
-    mcs_buyercode: "ACN202605280000"
+    mcs_buyercode: "0000016233" // 客户编号（mcs_sapnumber）
 };
 Xrm.WebApi.online.execute(request).then(
     function (result) {
@@ -1032,7 +1032,7 @@
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="4" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>客户编码</t>
+          <t>客户编码（客户编号，SAP 编码；与 816 授信池/风险敞口/厂端授信接口同一口径）</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>mcs_customermasterdata.mcs_accountnumber</t>
+          <t>mcs_customermasterdata.mcs_sapnumber</t>
         </is>
       </c>
     </row>
@@ -1641,17 +1641,17 @@
         <is>
           <t>[
   {
-    "tradeTermId": "TC26062502",
+    "tradeTermId": "TC2608140001",
     "buId": "BU-1018",
-    "buName": "CONCRETE MACHINERY BU/泵路海外营销公司",
-    "subId": "A000025",
-    "subName": "China-SH",
-    "countryCode": "1,001,KT",
-    "countryName": "南非,中国,Kertdiva",
-    "typeId": "01,02",
-    "typeName": "燃油牵引车,电动牵引车",
-    "buyerGrade": "A/S",
-    "downPay": 0.4000000000,
+    "buName": null,
+    "subId": "SUB-001",
+    "subName": null,
+    "countryCode": "",
+    "countryName": "",
+    "typeId": "",
+    "typeName": "",
+    "buyerGrade": "C",
+    "downPay": 0.3000000000,
     "payTerm": 30,
     "payFreq": 30
   }
@@ -1679,7 +1679,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>多产品线查询示例（UAT 实测，2026-07-28）</t>
+          <t>多产品线查询示例（UAT 实测，2026-07-28；mcs_buyercode 为旧口径流水号值，待按客户编号重测更新）</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1747,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>接口会根据 mcs_buyercode 查询客户主数据，自动计算客户分类代码。</t>
+          <t>接口会根据 mcs_buyercode 按客户编号（mcs_customermasterdata.mcs_sapnumber）查询客户主数据，自动计算客户分类代码。</t>
         </is>
       </c>
       <c r="B2" s="6" t="n"/>
